--- a/reports/pdf_rolling5_20260902.xlsx
+++ b/reports/pdf_rolling5_20260902.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,489억   ·   현금 69억(1.5%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 9종목  /  매도 13종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,489억   ·   현금 35억(0.8%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 9종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1166,7 +1166,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,768억   ·   현금 25억(0.7%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 5종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,768억   ·   현금 12억(0.3%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1443,7 +1443,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억   ·   현금 88억(3.5%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 5종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억   ·   현금 44억(1.8%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 5종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1752,7 +1752,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,141억   ·   현금 55억(2.5%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,141억   ·   현금 27억(1.3%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1985,7 +1985,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 3억(1.1%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 16종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 1억(0.5%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 16종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2403,23 +2403,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-88704000</v>
+        <v>-79200000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.48%→3.15%</t>
+          <t>2.76%→2.46%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>107→97</t>
+          <t>95→85</t>
         </is>
       </c>
     </row>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-79200000</v>
+        <v>-88704000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.46%</t>
+          <t>3.48%→3.15%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>95→85</t>
+          <t>107→97</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 535억   ·   현금 8억(1.4%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 535억   ·   현금 4억(0.7%)      오늘 2026-09-02  vs  5일전 2026-08-26      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B66" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260902.xlsx
+++ b/reports/pdf_rolling5_20260902.xlsx
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1055750000</v>
+        <v>-793350000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.16%</t>
+          <t>2.97%→2.86%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>59→49</t>
+          <t>171→161</t>
         </is>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-793350000</v>
+        <v>-1055750000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>2.97%→2.86%</t>
+          <t>1.42%→1.16%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>171→161</t>
+          <t>59→49</t>
         </is>
       </c>
     </row>
@@ -1087,23 +1087,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-389090000</v>
+        <v>-99220000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.33%</t>
+          <t>0.63%→0.64%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1115,23 +1115,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-99220000</v>
+        <v>-389090000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.64%</t>
+          <t>1.46%→1.33%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -2570,23 +2570,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>31802400</v>
+        <v>36187200</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.10%</t>
+          <t>0.80%→0.93%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>59→66</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G61" s="17" t="n"/>
@@ -2598,23 +2598,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>36187200</v>
+        <v>31802400</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.80%→0.93%</t>
+          <t>0.98%→1.10%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>59→66</t>
         </is>
       </c>
       <c r="G62" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260902.xlsx
+++ b/reports/pdf_rolling5_20260902.xlsx
@@ -1087,23 +1087,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-99220000</v>
+        <v>-389090000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.64%</t>
+          <t>1.46%→1.33%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -1115,23 +1115,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-389090000</v>
+        <v>-99220000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.33%</t>
+          <t>0.63%→0.64%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -2403,23 +2403,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-79200000</v>
+        <v>-88704000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.46%</t>
+          <t>3.48%→3.15%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>95→85</t>
+          <t>107→97</t>
         </is>
       </c>
     </row>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-88704000</v>
+        <v>-79200000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.48%→3.15%</t>
+          <t>2.76%→2.46%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>107→97</t>
+          <t>95→85</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260902.xlsx
+++ b/reports/pdf_rolling5_20260902.xlsx
@@ -1087,23 +1087,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-389090000</v>
+        <v>-99220000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.33%</t>
+          <t>0.63%→0.64%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1115,23 +1115,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-99220000</v>
+        <v>-389090000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.64%</t>
+          <t>1.46%→1.33%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -2570,23 +2570,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>36187200</v>
+        <v>31802400</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>0.80%→0.93%</t>
+          <t>0.98%→1.10%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>59→66</t>
         </is>
       </c>
       <c r="G61" s="17" t="n"/>
@@ -2598,23 +2598,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>31802400</v>
+        <v>36187200</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.10%</t>
+          <t>0.80%→0.93%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>59→66</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G62" s="17" t="n"/>
